--- a/s-s-event-bogor/sessions/day-2/clinic/tourism/otsa_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/tourism/otsa_exercise.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +68,14 @@
       <color rgb="00717171"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +92,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B9C7B"/>
+        <bgColor rgb="003B9C7B"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,6 +141,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,6 +510,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000A5455"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ocean Accounting Clinic: OTSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Exercise Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>How to use this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>This exercise helps you practice calculating an Ocean Tourism Satellite Account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>The Exercise sheet contains:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - National tourism data (arrivals, expenditure, GVA, employment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Visitor survey data on coastal/marine motivation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Yellow cells: fill these in with your calculations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>The Answers sheet shows the correct values in green cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>What you are calculating:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Tourism partial: the share of total tourism that is coastal/ocean-related</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Weighted partial: accounts for different spending levels between visitor types</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (international visitors spend 2.5x more per trip than domestic visitors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Coastal tourism indicators: arrivals, expenditure, GVA, and employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Formula: Coastal value = National value x Tourism partial</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="003B9C7B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -514,6 +667,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -593,6 +747,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -637,6 +792,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -660,6 +817,7 @@
       </c>
       <c r="B20" s="5" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -683,6 +841,7 @@
       </c>
       <c r="B24" s="5" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -693,7 +852,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Coastal tourism expenditure (USD M)</t>
+          <t>Coastal tourism expenditure (USD million)</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
@@ -701,7 +860,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Coastal tourism GVA (USD M)</t>
+          <t>Coastal tourism GVA (USD million)</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
@@ -727,7 +886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00006100"/>
@@ -748,6 +907,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -891,6 +1051,504 @@
           <t>(82.5 / 5,000 x 100)</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003B9C7B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Glossary of Terms and Abbreviations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Term / Abbreviation</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Gross Value Added</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Total output minus intermediate consumption. The value an industry adds to the economy.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Currency (e.g., USD, local currency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Total value of goods and services produced in a country. Sum of GVA across all industries plus taxes minus subsidies.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Intermediate Consumption</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>The value of goods and services consumed as inputs during production (e.g., fuel, raw materials, purchased services). Does not include fixed assets.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Gross Output</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Total value of goods and services produced by an industry before deducting input costs. Also called gross sales or turnover.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SUT</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Supply-Use Tables</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Statistical tables from the national accounts showing what each industry produces (supply) and what each industry consumes (use). Published by the National Statistical Office.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>System of National Accounts</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>The international statistical standard for measuring economic activity. Published by the UN. The basis for GDP calculation.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>SEEA-EA</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>System of Environmental-Economic Accounting - Ecosystem Accounting</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>The international statistical standard for measuring ecosystems, their condition, and the services they provide.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>OESA</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ocean Economy Satellite Account</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>A satellite account that reorganizes national accounts to identify the market-based ocean economy. Reports GDP-compatible indicators.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>OTSA</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ocean Tourism Satellite Account</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>A satellite account focused on coastal and marine tourism's economic contribution. A subset of OESA.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Ocean Economy Partial</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>The share (0 to 1) of a mixed industry's output that is ocean-related. For example, if 30% of construction is coastal, the partial is 0.30.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Proportion (0 to 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Condition Index</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>A normalized score from 0 (fully degraded) to 1 (reference/healthy condition). Used in SEEA-EA condition accounts.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Index (0 to 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>NCP</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Net Carbon Production</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>The rate at which an ecosystem sequesters carbon dioxide per unit area per year.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Mg CO2/ha/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>SCC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Social Cost of Carbon</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>An estimate of the economic damage caused by emitting one additional tonne of CO2. Used to value carbon sequestration.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>USD per Mg CO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Mg CO2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Megagrams of CO2</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Metric tonnes of carbon dioxide. 1 Mg = 1 tonne = 1,000 kg.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ha</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Hectares</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Unit of area. 1 hectare = 10,000 square metres = 0.01 square kilometres.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Kilograms per year</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Physical quantity measured in kilograms over one year.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Mass per time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>USD million</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>United States Dollars, millions</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Monetary values expressed in millions of US dollars. For example, USD 132.5 million = USD 132,500,000.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>R million</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>South African Rand, millions</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Monetary values in the South Africa example are in millions of Rand.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ISIC</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>International Standard Industrial Classification</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>The UN classification system for economic activities. Used to map industries to ocean economy groups.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>SIC</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Standard Industrial Classification</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>National classification system for economic activities. Varies by country but based on ISIC.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Exclusive Economic Zone</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Maritime zone extending 200 nautical miles from a country's coastline, within which the country has rights to marine resources.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Red-Amber-Green</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>A confidence rating system. Green = high confidence (direct evidence). Amber = moderate (proxy data). Red = low (sparse evidence).</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
